--- a/자료/결과/Ortools/S1_1_균등/overdue_list.xlsx
+++ b/자료/결과/Ortools/S1_1_균등/overdue_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\choih\Desktop\연구\PDPTW\자료\결과\Ortools\S1_1_균등\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BB50D8A-FD69-421C-A2F4-9A7A53A8CECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD125921-DBAA-42BB-8854-7FE244544298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="9" xr2:uid="{F76313A7-D45F-4662-A3D2-F6EA2892E64A}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{F76313A7-D45F-4662-A3D2-F6EA2892E64A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="588">
   <si>
     <t>batch_id</t>
   </si>
@@ -1809,6 +1809,9 @@
   </si>
   <si>
     <t>B4223</t>
+  </si>
+  <si>
+    <t>서울역</t>
   </si>
 </sst>
 </file>
@@ -2195,7 +2198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5DB468-9839-462F-B151-148FDBB2D8FA}">
-  <dimension ref="A1:T166"/>
+  <dimension ref="A1:T167"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
@@ -9518,6 +9521,11 @@
       </c>
       <c r="T166" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C167" t="s">
+        <v>587</v>
       </c>
     </row>
   </sheetData>
